--- a/tests/fixtures/pilot/1clinical_goals_90000001_Manual.xlsx
+++ b/tests/fixtures/pilot/1clinical_goals_90000001_Manual.xlsx
@@ -687,13 +687,13 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>95</v>
+        <v>0.95</v>
       </c>
       <c r="H6" t="n">
-        <v>95</v>
+        <v>4180</v>
       </c>
       <c r="I6" t="n">
-        <v>97.2</v>
+        <v>0.972</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
